--- a/vault-dalarna-university/04 ISLL/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,329 +472,3812 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GIT2T6</t>
+          <t>AR1003</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>ARA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla studentens kunskaper om den moderna arabiska novellen under 1900- och 2000-talet.…</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2T6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GPR3GM</t>
+          <t>AEN25H</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>AEN25J</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande…</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>AEN26E</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att förbereda studenten för skrivandet av ett litteraturvetenskapligt examensarbete på ava…</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN26E</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>EN1129</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter avslutad kurs ska kunna:…</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>EN2043</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande fördjupar sina…</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>EN2046</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det…</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TY2004</t>
+          <t>EN2047</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>EN3029</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter avslutad kurs skall kunna:…</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>EN3071</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen vänder sig till lärarstuderande och bygger på kursen _Engelska IIl, inklusive examensarbete 1 för ämneslärarexame…</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>GEN222</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande…</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>GEN28Q</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper om engelskämnets ämnesteoretiska och didaktiska …</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GEN2BJ</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande efter avslutad kurs visar en god muntlig och skriftlig kommunikativ förmå…</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>GEN2BK</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>GEN2JG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande utvecklar grundläggande språkdidaktiska kunskaper i engelska.…</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>GEN2LD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>GEN2QW</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande utvecklar grundläggande språkdidaktiska kunskaper i engelska.…</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>GEN2RZ</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet för kursen är att förbereda studenterna för muntliga presentationer i akademiska och professionel…</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>GEN2S2</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda studenterna för arbetsmarknaden genom att utveckla deras förståelse av muntlig…</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GEN379</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion i och förberedelse för sin blivande yrkesroll som engelsklärare…</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>GEN37A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att ge en omfattande introduktion till studier i engelska på universitetsnivå.…</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>GEN3CM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar goda kunskaper i det engelska språket, om engelskspråkig litteratur och om de…</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DG</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten vidareutvecklar sina kunskaper om det engelska språket och om engelskämnets ve…</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>GEN3DK</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper om engelskämnets litteraturvetenskapliga grund. Ytter…</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GEN3K3</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ENA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten vidareutvecklar sina kunskaper om det engelska språket och om engelskämnets ve…</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>AFR24A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i franska och sin teoretiska medvetenhet i…</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>AFR24B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AFR24Z</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att förbereda den studerande inför uppgiften att skriva ett språkvetenskapligt eller litte…</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>AFR2A8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper om talad franska och dess olika varianter vad gäller ut…</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>GFR27R</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten vidareutvecklar sina kunskaper om fransk litteratur och fördjupar förmågan till litterä…</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>GFR27S</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt och muntligt på franska i arbetslivet. Efter avsluta…</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>GFR2A7</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla färdigheter i att kommunicera muntligt på franska.…</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>GFR2A8</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt på franska.…</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>GFR2AB</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla kunskaper om modern franskspråkig litteratur.…</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2AB</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>GFR2R4</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>GFR2W9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>GFR2WA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket, om franskspråkig kultur och li…</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>GFR3BS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i franska och sin teoretiska medvetenhet i…</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>GFR3CX</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande vidareutvecklar sina kunskaper om fransk litteratur och fördjupar förmågan till li…</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CX</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>GFR3D2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket samt om franskspråkig kultur oc…</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>GFR3D3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>GFR3DL</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar goda kunskaper i och om det franska språket samt om franskspråki…</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>GFR3HK</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HK</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GFR3HM</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket samt om franskspråkig kultur oc…</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GFR3HN</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GIT2Y9</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om familjeskildringar i italiensk skönlitteratur.…</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GIT2YA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om hur livet i Italien kring det andra världskriget sk…</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GIT2YB</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om italiensk skönlitteratur från det nya millenniet.…</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GIT2YC</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att studenten tillägnar sig kunskaper om italiensk skönlitteratur från 1900-talet.…</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GIT2YD</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att studenten tillägnar sig kunskaper om kvinnoskildringar i italiensk skönlitteratur.…</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>GIT2YE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om barn- och ungdomsskildringar i italiensk skönlitter…</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>AKI25K</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GKI27M</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla…</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>GKI2MY</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i det kinesiska språket, vilket förbere…</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GKI2PY</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att hjälpa studenterna att befästa de kunskaper de tillgodogjort sig på kurserna på lägre nivå i kine…</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GKI2W3</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ämnar att ge den studerande grundläggande kunskaper i det kinesiska språket, vilket förbereder den studerande inf…</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>GKI3CE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka och vidareutveckla den studerandes språkfärdighet i kinesiska. Kursen ämnar även …</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>KI1030</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>KIA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att stärka och ytterligare utveckla studenternas språkfärdighet inom det kinesiska språket, i de fyra…</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GPR3GM</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GPR3GN</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GPR3GP</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GRY2YW</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren efter avslutad kurs har utvecklat kunskaper, färdigheter och förhållnings…</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2YW</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GRY325</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>RYA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om den ryska operans utveckling från 1917 och fra…</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>ASP25D</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i spanska och sin teoretiska medvetenhet i…</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>ASP25E</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i spanska och sin teoretiska medvetenhet i…</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GSP28C</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur och spansk ling…</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GSP2FQ</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GSP2FR</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokumen…</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>GSP2JH</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande…</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GSP2SK</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten utvecklar kunskaper om den spansktalande världens kultur och samhällsförhållanden samt …</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GSP2W6</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>GSP2W7</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen…</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W7</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>GSP2W8</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion i och förberedelse för sin blivande yrkesroll som spansklärare …</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>SP1051</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål…</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>SP1052</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar goda…</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>SP1053</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>SP2021</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Genom studiet av relevant litteraturteori och -historia utvecklar studenten sin förmåga att analysera och kritiskt grans…</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>SP2022</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>SP2023</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SPA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>GSS2FK</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>GSS2G8</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina…</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>GSS2GP</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina didaktiska kunskaper i arabiska som modersmål.…</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>GSS2J5</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar kunskaper och färdigheter för att kunna kommunicera…</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>GSS2JA</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade och vidgade kunskaper i svenska som andrasp…</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>GSS2L2</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att ge grundläggande kunskaper i arabisk grammatik och litteratur med didaktiskt fokus.…</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>GSS2MN</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>GSS2QV</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GSS2XE</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade och vidgade kunskaper i svenska som andrasp…</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>GSS35H</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i arabiska som modersmål med didaktiskt fokus.…</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>GSS39P</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande orienterar sig om andraspråksforskning och forskning om svenska som and…</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>GSS39Q</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande fördjupar sig i ett kunskapsområde inom ramen för andraspråksforskning …</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>GSS39R</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BL</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är indelade per delkurs.…</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>GSS3BN</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>GSS3C7</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GSS3H8</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HB</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i ämnet modersmål med didaktiskt fokus. Därutöve…</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HG</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>GSS3HJ</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>SS1085</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper inom Svenska som andr…</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>SS2009</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Se respektive delkurs…</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>ASV29Z</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>ASV2A2</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>GSV2P9</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet…</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZU</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZV</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZW</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>GSV2ZX</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DD</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper om språkliga och innehållsliga möns…</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DE</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande uppnår fördjupade kunskaper om språk och skönlitteratur i relation till s…</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>GSV3DF</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bredda sitt kunnande om forsknings- och utvecklingsarbete inom litter…</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GSV3JE</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SVE</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar teoretiska och didaktiska kunskaper om barns språk-, l…</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>ATY255</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>ATY256</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>ATY2B8</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i teorier kring genus och identitet och hur…</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>GTY23C</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till tyskspråkig barn- och ungdomslitteratur med tonvikt på samtida texter. Litteratur i olik…</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>GTY2N5</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper in…</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>GTY2ST</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i tysk grammatik och färdigheter i …</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>GTY2SU</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i allmän och tysk grammatik samt fä…</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SU</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>GTY2SW</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska förvärva en inblick i modern tyskspråkig litteratur. Efter genomgången kurs ska…</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>GTY2SY</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla sitt kreativa skrivande och sin förmåga att uttrycka sig korrekt, vari…</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SY</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GTY2SZ</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska. Den studerande…</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>GTY2W5</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt på…</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2W5</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>GTY369</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska samt förvärva e…</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY369</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CT</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det tyska språket, om tyskspråkig kultur och litter…</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>GTY3CU</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska…</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>GTY3J9</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska…</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>GTY3JB</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studenten fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper inom ty…</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>TY1038</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i språkdidaktik och att de förbereder sig för sin fra…</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>TY1049</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska lära känna ett antal tyskspråkiga litterära verk från upplysningen och fram till …</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>TY1050</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande skall befästa och ytterligare förbättra förmågan att använda det tyska språket i sk…</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>TY1066</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokument samt att de…</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>TY1069</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förvärva en djupare inblick i tysk språk- och kulturhistoria och skaffa sig en…</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>TY1073</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förbättra sin förmåga att uttrycka sig ledigt och korrekt på tyska. Den studer…</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>TY2004</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna tillägnar sig en ökad litteraturvetenskaplig orientering med utgångspunkt i den tysks…</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att studenterna ytterligare ska uppöva sin förmåga till vetenskapligt arbete.…</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva vidgade insikter i den moderna tyska språkvetenskapens utveckling. Kurse…</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>TY3012</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva väsentligt fördjupade insikter i det tyska språkets struktur och variati…</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
           <t>TY3013</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Saknar introfras</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Saknar introfras före lärandemålen</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i den tyska moderna kvinnolitteraturen. Det…</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att närmare belysa och problematisera begreppen intertextualitet och intermedialitet. Med utgångspunkt …</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>TY3016</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva fördjupade insikter om…</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E13"/>
+  <autoFilter ref="A1:E142"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -820,6 +4303,264 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$142</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2008-10-23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla studentens kunskaper om den moderna arabiska novellen under 1900- och 2000-talet.…</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AR1003</t>
         </is>
@@ -509,15 +531,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande…</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25H</t>
         </is>
@@ -536,15 +564,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande…</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN25J</t>
         </is>
@@ -563,15 +597,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2020-12-23</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att förbereda studenten för skrivandet av ett litteraturvetenskapligt examensarbete på ava…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AEN26E</t>
         </is>
@@ -590,15 +630,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2015-10-09</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter avslutad kurs ska kunna:…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN1129</t>
         </is>
@@ -617,15 +663,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2015-03-16</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande fördjupar sina…</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2043</t>
         </is>
@@ -644,15 +696,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2046</t>
         </is>
@@ -671,15 +729,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2016-02-05</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN2047</t>
         </is>
@@ -698,15 +762,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2008-01-11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande efter avslutad kurs skall kunna:…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3029</t>
         </is>
@@ -725,15 +799,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2015-03-12</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen vänder sig till lärarstuderande och bygger på kursen _Engelska IIl, inklusive examensarbete 1 för ämneslärarexame…</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=EN3071</t>
         </is>
@@ -752,15 +832,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+          <t>2018-03-22</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande…</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN222</t>
         </is>
@@ -779,15 +865,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2019-03-21</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>2023-03-17</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper om engelskämnets ämnesteoretiska och didaktiska …</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN28Q</t>
         </is>
@@ -806,15 +902,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande efter avslutad kurs visar en god muntlig och skriftlig kommunikativ förmå…</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BJ</t>
         </is>
@@ -833,15 +935,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>2019-09-20</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2BK</t>
         </is>
@@ -860,15 +968,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande utvecklar grundläggande språkdidaktiska kunskaper i engelska.…</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2JG</t>
         </is>
@@ -887,15 +1001,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2020-12-23</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar…</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2LD</t>
         </is>
@@ -914,15 +1034,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande utvecklar grundläggande språkdidaktiska kunskaper i engelska.…</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2QW</t>
         </is>
@@ -941,15 +1067,21 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet för kursen är att förbereda studenterna för muntliga presentationer i akademiska och professionel…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2RZ</t>
         </is>
@@ -968,15 +1100,21 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att förbereda studenterna för arbetsmarknaden genom att utveckla deras förståelse av muntlig…</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN2S2</t>
         </is>
@@ -995,15 +1133,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion i och förberedelse för sin blivande yrkesroll som engelsklärare…</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN379</t>
         </is>
@@ -1022,15 +1166,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att ge en omfattande introduktion till studier i engelska på universitetsnivå.…</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN37A</t>
         </is>
@@ -1049,15 +1199,21 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar goda kunskaper i det engelska språket, om engelskspråkig litteratur och om de…</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3CM</t>
         </is>
@@ -1076,15 +1232,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten vidareutvecklar sina kunskaper om det engelska språket och om engelskämnets ve…</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DG</t>
         </is>
@@ -1103,15 +1265,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten fördjupar sina kunskaper om engelskämnets litteraturvetenskapliga grund. Ytter…</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3DK</t>
         </is>
@@ -1130,15 +1298,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten vidareutvecklar sina kunskaper om det engelska språket och om engelskämnets ve…</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3K3</t>
         </is>
@@ -1157,15 +1331,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i franska och sin teoretiska medvetenhet i…</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
@@ -1184,15 +1364,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
@@ -1211,15 +1397,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2020-03-09</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att förbereda den studerande inför uppgiften att skriva ett språkvetenskapligt eller litte…</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
         </is>
@@ -1238,15 +1430,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper om talad franska och dess olika varianter vad gäller ut…</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
@@ -1265,15 +1463,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2019-03-07</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten vidareutvecklar sina kunskaper om fransk litteratur och fördjupar förmågan till litterä…</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
@@ -1292,15 +1496,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+          <t>2019-03-11</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt och muntligt på franska i arbetslivet. Efter avsluta…</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
         </is>
@@ -1319,15 +1529,21 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla färdigheter i att kommunicera muntligt på franska.…</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A7</t>
         </is>
@@ -1346,15 +1562,21 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt på franska.…</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
@@ -1373,15 +1595,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2019-06-17</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla kunskaper om modern franskspråkig litteratur.…</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2AB</t>
         </is>
@@ -1400,15 +1628,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2021-09-06</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
@@ -1427,15 +1661,21 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
@@ -1454,15 +1694,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket, om franskspråkig kultur och li…</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
@@ -1481,15 +1727,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i franska och sin teoretiska medvetenhet i…</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
@@ -1508,15 +1760,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande vidareutvecklar sina kunskaper om fransk litteratur och fördjupar förmågan till li…</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CX</t>
         </is>
@@ -1535,15 +1793,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket samt om franskspråkig kultur oc…</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
@@ -1562,15 +1826,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
@@ -1589,15 +1859,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar goda kunskaper i och om det franska språket samt om franskspråki…</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
@@ -1616,15 +1892,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HK</t>
         </is>
@@ -1643,15 +1925,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket samt om franskspråkig kultur oc…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
@@ -1670,15 +1958,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
@@ -1697,15 +1991,25 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om familjeskildringar i italiensk skönlitteratur.…</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
@@ -1724,15 +2028,25 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om hur livet i Italien kring det andra världskriget sk…</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
@@ -1751,15 +2065,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om italiensk skönlitteratur från det nya millenniet.…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
@@ -1778,15 +2102,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att studenten tillägnar sig kunskaper om italiensk skönlitteratur från 1900-talet.…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
@@ -1805,15 +2139,25 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att studenten tillägnar sig kunskaper om kvinnoskildringar i italiensk skönlitteratur.…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
@@ -1832,15 +2176,25 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2022-11-11</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om barn- och ungdomsskildringar i italiensk skönlitter…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YE</t>
         </is>
@@ -1859,15 +2213,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2020-03-12</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
@@ -1886,15 +2246,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2019-03-08</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla…</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
         </is>
@@ -1913,15 +2279,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2021-03-02</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i det kinesiska språket, vilket förbere…</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
@@ -1940,15 +2312,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+          <t>2021-05-03</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att hjälpa studenterna att befästa de kunskaper de tillgodogjort sig på kurserna på lägre nivå i kine…</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
@@ -1967,15 +2345,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen ämnar att ge den studerande grundläggande kunskaper i det kinesiska språket, vilket förbereder den studerande inf…</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
@@ -1994,15 +2378,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka och vidareutveckla den studerandes språkfärdighet i kinesiska. Kursen ämnar även …</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
@@ -2021,15 +2411,25 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2011-02-01</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att stärka och ytterligare utveckla studenternas språkfärdighet inom det kinesiska språket, i de fyra…</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
@@ -2048,15 +2448,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
         </is>
@@ -2075,15 +2481,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
@@ -2102,15 +2514,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
@@ -2129,15 +2547,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2022-11-29</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren efter avslutad kurs har utvecklat kunskaper, färdigheter och förhållnings…</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2YW</t>
         </is>
@@ -2156,15 +2580,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om den ryska operans utveckling från 1917 och fra…</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
@@ -2183,15 +2613,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i spanska och sin teoretiska medvetenhet i…</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
@@ -2210,15 +2646,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i spanska och sin teoretiska medvetenhet i…</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
@@ -2237,15 +2679,21 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
+          <t>2019-03-13</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur och spansk ling…</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
@@ -2264,15 +2712,25 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
@@ -2291,15 +2749,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokumen…</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
@@ -2318,15 +2782,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2020-09-21</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande…</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
@@ -2345,15 +2815,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2021-12-10</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten utvecklar kunskaper om den spansktalande världens kultur och samhällsförhållanden samt …</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SK</t>
         </is>
@@ -2372,15 +2848,21 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
         </is>
@@ -2399,15 +2881,21 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen…</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W7</t>
         </is>
@@ -2426,15 +2914,25 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion i och förberedelse för sin blivande yrkesroll som spansklärare …</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
@@ -2453,15 +2951,21 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål…</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
@@ -2480,15 +2984,21 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar goda…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
@@ -2507,15 +3017,21 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
+          <t>2017-06-15</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
         </is>
@@ -2534,15 +3050,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Genom studiet av relevant litteraturteori och -historia utvecklar studenten sin förmåga att analysera och kritiskt grans…</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
@@ -2561,15 +3083,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
@@ -2588,15 +3116,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>2018-02-12</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
@@ -2615,15 +3149,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>2020-03-10</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
@@ -2642,15 +3182,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+          <t>2020-04-01</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina…</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
@@ -2669,15 +3215,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
+          <t>2020-04-27</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina didaktiska kunskaper i arabiska som modersmål.…</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
@@ -2696,15 +3248,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2020-09-09</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar kunskaper och färdigheter för att kunna kommunicera…</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
@@ -2723,15 +3281,21 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
+          <t>2020-09-14</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade och vidgade kunskaper i svenska som andrasp…</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
@@ -2750,15 +3314,21 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
+          <t>2020-12-01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att ge grundläggande kunskaper i arabisk grammatik och litteratur med didaktiskt fokus.…</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
@@ -2777,15 +3347,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
+          <t>2021-02-25</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
@@ -2804,15 +3380,21 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
+          <t>2021-06-30</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
@@ -2831,15 +3413,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
+          <t>2022-09-02</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade och vidgade kunskaper i svenska som andrasp…</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
@@ -2858,15 +3446,21 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i arabiska som modersmål med didaktiskt fokus.…</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
@@ -2885,15 +3479,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande orienterar sig om andraspråksforskning och forskning om svenska som and…</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
@@ -2912,15 +3512,21 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande fördjupar sig i ett kunskapsområde inom ramen för andraspråksforskning …</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
         </is>
@@ -2939,15 +3545,21 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
@@ -2966,15 +3578,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är indelade per delkurs.…</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
@@ -2993,15 +3611,21 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
@@ -3020,15 +3644,21 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
@@ -3047,15 +3677,21 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
@@ -3074,15 +3710,21 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i ämnet modersmål med didaktiskt fokus. Därutöve…</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
@@ -3101,15 +3743,21 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
@@ -3128,15 +3776,21 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
@@ -3155,15 +3809,21 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
+          <t>2015-03-03</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper inom Svenska som andr…</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
@@ -3182,15 +3842,21 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Se respektive delkurs…</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
@@ -3209,15 +3875,21 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
@@ -3236,15 +3908,21 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
+          <t>2023-12-04</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
@@ -3263,15 +3941,21 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
+          <t>2021-04-12</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet…</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
         </is>
@@ -3290,15 +3974,21 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
@@ -3317,15 +4007,21 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
@@ -3344,15 +4040,21 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
@@ -3371,15 +4073,21 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
+          <t>2023-01-23</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
@@ -3398,15 +4106,21 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper om språkliga och innehållsliga möns…</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
@@ -3425,15 +4139,21 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande uppnår fördjupade kunskaper om språk och skönlitteratur i relation till s…</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
@@ -3452,15 +4172,21 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
+          <t>2025-01-13</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bredda sitt kunnande om forsknings- och utvecklingsarbete inom litter…</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
@@ -3479,15 +4205,21 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar teoretiska och didaktiska kunskaper om barns språk-, l…</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
@@ -3506,15 +4238,21 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
@@ -3533,15 +4271,21 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
+          <t>2020-03-11</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
@@ -3560,15 +4304,21 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i teorier kring genus och identitet och hur…</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
@@ -3587,15 +4337,21 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
+          <t>2018-06-05</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till tyskspråkig barn- och ungdomslitteratur med tonvikt på samtida texter. Litteratur i olik…</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
@@ -3614,15 +4370,21 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
+          <t>2021-03-04</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper in…</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
@@ -3641,15 +4403,21 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i tysk grammatik och färdigheter i …</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
@@ -3668,15 +4436,21 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i allmän och tysk grammatik samt fä…</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SU</t>
         </is>
@@ -3695,15 +4469,21 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska förvärva en inblick i modern tyskspråkig litteratur. Efter genomgången kurs ska…</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
         </is>
@@ -3722,15 +4502,21 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla sitt kreativa skrivande och sin förmåga att uttrycka sig korrekt, vari…</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SY</t>
         </is>
@@ -3749,15 +4535,21 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska. Den studerande…</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SZ</t>
         </is>
@@ -3776,15 +4568,21 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt på…</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2W5</t>
         </is>
@@ -3803,15 +4601,21 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska samt förvärva e…</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY369</t>
         </is>
@@ -3830,15 +4634,21 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det tyska språket, om tyskspråkig kultur och litter…</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
@@ -3857,15 +4667,21 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska…</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
@@ -3884,15 +4700,21 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska…</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
@@ -3911,15 +4733,21 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studenten fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper inom ty…</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
@@ -3938,15 +4766,25 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2011-10-10</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>2020-07-02</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i språkdidaktik och att de förbereder sig för sin fra…</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
         </is>
@@ -3965,15 +4803,25 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska lära känna ett antal tyskspråkiga litterära verk från upplysningen och fram till …</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
@@ -3992,15 +4840,25 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande skall befästa och ytterligare förbättra förmågan att använda det tyska språket i sk…</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
@@ -4019,15 +4877,25 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokument samt att de…</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
@@ -4046,15 +4914,21 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förvärva en djupare inblick i tysk språk- och kulturhistoria och skaffa sig en…</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
@@ -4073,15 +4947,21 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
+          <t>2017-02-13</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förbättra sin förmåga att uttrycka sig ledigt och korrekt på tyska. Den studer…</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
@@ -4100,15 +4980,25 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2008-05-29</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna tillägnar sig en ökad litteraturvetenskaplig orientering med utgångspunkt i den tysks…</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
         </is>
@@ -4127,15 +5017,25 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att studenterna ytterligare ska uppöva sin förmåga till vetenskapligt arbete.…</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
@@ -4154,15 +5054,25 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva vidgade insikter i den moderna tyska språkvetenskapens utveckling. Kurse…</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
@@ -4181,15 +5091,25 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva väsentligt fördjupade insikter i det tyska språkets struktur och variati…</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
@@ -4208,15 +5128,25 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i den tyska moderna kvinnolitteraturen. Det…</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
@@ -4235,15 +5165,25 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-11-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att närmare belysa och problematisera begreppen intertextualitet och intermedialitet. Med utgångspunkt …</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
         </is>
@@ -4262,305 +5202,315 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2014-01-27</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva fördjupade insikter om…</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E142"/>
+  <autoFilter ref="A1:G142"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId172"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId174"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId176"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G90" r:id="rId178"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G91" r:id="rId180"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G92" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G93" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G94" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G95" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G96" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G97" r:id="rId192"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G98" r:id="rId194"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G99" r:id="rId196"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G100" r:id="rId198"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G101" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G102" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G103" r:id="rId204"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G104" r:id="rId206"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G105" r:id="rId208"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G106" r:id="rId210"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G107" r:id="rId212"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G108" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G109" r:id="rId216"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G110" r:id="rId218"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G111" r:id="rId220"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G112" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G113" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G114" r:id="rId226"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A115" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G115" r:id="rId228"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A116" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G116" r:id="rId230"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G117" r:id="rId232"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A118" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G118" r:id="rId234"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A119" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G119" r:id="rId236"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A120" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G120" r:id="rId238"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A121" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G121" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G122" r:id="rId242"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A123" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E123" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G123" r:id="rId244"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A124" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E124" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G124" r:id="rId246"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A125" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E125" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G125" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E126" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G126" r:id="rId250"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A127" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E127" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G127" r:id="rId252"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A128" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E128" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G128" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A129" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E129" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G129" r:id="rId256"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A130" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E130" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G130" r:id="rId258"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A131" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E131" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G131" r:id="rId260"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A132" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E132" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G132" r:id="rId262"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E133" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G133" r:id="rId264"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A134" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E134" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G134" r:id="rId266"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A135" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E135" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G135" r:id="rId268"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E136" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G136" r:id="rId270"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A137" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E137" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G137" r:id="rId272"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A138" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E138" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G138" r:id="rId274"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A139" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E139" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G139" r:id="rId276"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A140" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E140" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G140" r:id="rId278"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A141" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E141" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$143</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1321,17 +1321,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>AFR24A</t>
+          <t>GEN3KC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ENA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1342,19 +1342,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i franska och sin teoretiska medvetenhet i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper om engelskämnets ämnesteoretiska och didaktiska …</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GEN3KC</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AFR24B</t>
+          <t>AFR24A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1375,19 +1375,19 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i franska och sin teoretiska medvetenhet i…</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24A</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AFR24Z</t>
+          <t>AFR24B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2020-03-09</t>
+          <t>2020-02-26</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1408,19 +1408,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att förbereda den studerande inför uppgiften att skriva ett språkvetenskapligt eller litte…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24B</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>AFR2A8</t>
+          <t>AFR24Z</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2020-03-09</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
@@ -1441,19 +1441,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper om talad franska och dess olika varianter vad gäller ut…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att förbereda den studerande inför uppgiften att skriva ett språkvetenskapligt eller litte…</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR24Z</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GFR27R</t>
+          <t>AFR2A8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2023-12-08</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
@@ -1474,19 +1474,19 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten vidareutvecklar sina kunskaper om fransk litteratur och fördjupar förmågan till litterä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper om talad franska och dess olika varianter vad gäller ut…</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AFR2A8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GFR27S</t>
+          <t>GFR27R</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2019-03-11</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
@@ -1507,19 +1507,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt och muntligt på franska i arbetslivet. Efter avsluta…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten vidareutvecklar sina kunskaper om fransk litteratur och fördjupar förmågan till litterä…</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27R</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>GFR2A7</t>
+          <t>GFR27S</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2019-06-17</t>
+          <t>2019-03-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
@@ -1540,19 +1540,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla färdigheter i att kommunicera muntligt på franska.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt och muntligt på franska i arbetslivet. Efter avsluta…</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR27S</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>GFR2A8</t>
+          <t>GFR2A7</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1573,19 +1573,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt på franska.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla färdigheter i att kommunicera muntligt på franska.…</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GFR2AB</t>
+          <t>GFR2A8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1606,19 +1606,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla kunskaper om modern franskspråkig litteratur.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt på franska.…</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2AB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2A8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GFR2R4</t>
+          <t>GFR2AB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2021-09-06</t>
+          <t>2019-06-17</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -1639,19 +1639,19 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla kunskaper om modern franskspråkig litteratur.…</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2AB</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GFR2W9</t>
+          <t>GFR2R4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-09-06</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
@@ -1672,19 +1672,19 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2R4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GFR2WA</t>
+          <t>GFR2W9</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1705,19 +1705,19 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket, om franskspråkig kultur och li…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2W9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GFR3BS</t>
+          <t>GFR2WA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1738,19 +1738,19 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i franska och sin teoretiska medvetenhet i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket, om franskspråkig kultur och li…</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR2WA</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GFR3CX</t>
+          <t>GFR3BS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1771,19 +1771,19 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande vidareutvecklar sina kunskaper om fransk litteratur och fördjupar förmågan till li…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i franska och sin teoretiska medvetenhet i…</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3BS</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GFR3D2</t>
+          <t>GFR3CX</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1804,19 +1804,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket samt om franskspråkig kultur oc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande vidareutvecklar sina kunskaper om fransk litteratur och fördjupar förmågan till li…</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3CX</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GFR3D3</t>
+          <t>GFR3D2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket samt om franskspråkig kultur oc…</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GFR3DL</t>
+          <t>GFR3D3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1870,19 +1870,19 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar goda kunskaper i och om det franska språket samt om franskspråki…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3D3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GFR3HK</t>
+          <t>GFR3DL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1903,19 +1903,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande utvecklar goda kunskaper i och om det franska språket samt om franskspråki…</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3DL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GFR3HM</t>
+          <t>GFR3HK</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1936,19 +1936,19 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket samt om franskspråkig kultur oc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HK</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GFR3HN</t>
+          <t>GFR3HM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,36 +1969,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det franska språket samt om franskspråkig kultur oc…</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HM</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GIT2Y9</t>
+          <t>GFR3HN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2023-12-18</t>
-        </is>
-      </c>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2006,19 +2002,19 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om familjeskildringar i italiensk skönlitteratur.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det franska språket och om franskspråkig litte…</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GFR3HN</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GIT2YA</t>
+          <t>GIT2Y9</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2043,19 +2039,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om hur livet i Italien kring det andra världskriget sk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om familjeskildringar i italiensk skönlitteratur.…</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2Y9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GIT2YB</t>
+          <t>GIT2YA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2080,19 +2076,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om italiensk skönlitteratur från det nya millenniet.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om hur livet i Italien kring det andra världskriget sk…</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GIT2YC</t>
+          <t>GIT2YB</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2117,19 +2113,19 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att studenten tillägnar sig kunskaper om italiensk skönlitteratur från 1900-talet.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om italiensk skönlitteratur från det nya millenniet.…</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YB</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GIT2YD</t>
+          <t>GIT2YC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2154,19 +2150,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att studenten tillägnar sig kunskaper om kvinnoskildringar i italiensk skönlitteratur.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att studenten tillägnar sig kunskaper om italiensk skönlitteratur från 1900-talet.…</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YC</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GIT2YE</t>
+          <t>GIT2YD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2191,32 +2187,36 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om barn- och ungdomsskildringar i italiensk skönlitter…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att studenten tillägnar sig kunskaper om kvinnoskildringar i italiensk skönlitteratur.…</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YD</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>GIT2YE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2020-03-12</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2224,19 +2224,19 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om barn- och ungdomsskildringar i italiensk skönlitter…</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT2YE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GKI27M</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2019-03-08</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2257,19 +2257,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GKI27M</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2019-03-08</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2290,19 +2290,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i det kinesiska språket, vilket förbere…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla…</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2323,19 +2323,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att hjälpa studenterna att befästa de kunskaper de tillgodogjort sig på kurserna på lägre nivå i kine…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i det kinesiska språket, vilket förbere…</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2356,19 +2356,19 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen ämnar att ge den studerande grundläggande kunskaper i det kinesiska språket, vilket förbereder den studerande inf…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att hjälpa studenterna att befästa de kunskaper de tillgodogjort sig på kurserna på lägre nivå i kine…</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2389,19 +2389,19 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka och vidareutveckla den studerandes språkfärdighet i kinesiska. Kursen ämnar även …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ämnar att ge den studerande grundläggande kunskaper i det kinesiska språket, vilket förbereder den studerande inf…</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2411,14 +2411,10 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2426,32 +2422,36 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att stärka och ytterligare utveckla studenternas språkfärdighet inom det kinesiska språket, i de fyra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka och vidareutveckla den studerandes språkfärdighet i kinesiska. Kursen ämnar även …</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GPR3GM</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2459,19 +2459,19 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att stärka och ytterligare utveckla studenternas språkfärdighet inom det kinesiska språket, i de fyra…</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GPR3GM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2497,14 +2497,14 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2530,24 +2530,24 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GRY2YW</t>
+          <t>GPR3GP</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -2558,19 +2558,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren efter avslutad kurs har utvecklat kunskaper, färdigheter och förhållnings…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2YW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GRY2YW</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2591,29 +2591,29 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om den ryska operans utveckling från 1917 och fra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren efter avslutad kurs har utvecklat kunskaper, färdigheter och förhållnings…</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2YW</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i spanska och sin teoretiska medvetenhet i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om den ryska operans utveckling från 1917 och fra…</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>ASP25D</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2662,14 +2662,14 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>ASP25E</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2019-03-13</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -2690,19 +2690,19 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur och spansk ling…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i spanska och sin teoretiska medvetenhet i…</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GSP28C</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2712,14 +2712,10 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
+          <t>2019-03-13</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2727,19 +2723,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur och spansk ling…</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2749,10 +2745,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2760,19 +2760,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokumen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -2793,19 +2793,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokumen…</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSP2SK</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2021-12-10</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2826,19 +2826,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten utvecklar kunskaper om den spansktalande världens kultur och samhällsförhållanden samt …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande…</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSP2W6</t>
+          <t>GSP2SK</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2859,19 +2859,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten utvecklar kunskaper om den spansktalande världens kultur och samhällsförhållanden samt …</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SK</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSP2W7</t>
+          <t>GSP2W6</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2892,19 +2892,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GSP2W7</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2917,11 +2917,7 @@
           <t>2022-04-28</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2023-11-02</t>
-        </is>
-      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2929,19 +2925,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion i och förberedelse för sin blivande yrkesroll som spansklärare …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen…</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2951,10 +2947,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2962,19 +2962,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion i och förberedelse för sin blivande yrkesroll som spansklärare …</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SP1052</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2995,19 +2995,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar goda…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål…</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SP1053</t>
+          <t>SP1052</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3028,19 +3028,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar goda…</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>SP1053</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3061,19 +3061,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Genom studiet av relevant litteraturteori och -historia utvecklar studenten sin förmåga att analysera och kritiskt grans…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3094,19 +3094,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Genom studiet av relevant litteraturteori och -historia utvecklar studenten sin förmåga att analysera och kritiskt grans…</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3132,24 +3132,24 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3160,19 +3160,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2020-03-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3193,19 +3193,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -3226,19 +3226,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina didaktiska kunskaper i arabiska som modersmål.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina…</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3259,19 +3259,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar kunskaper och färdigheter för att kunna kommunicera…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina didaktiska kunskaper i arabiska som modersmål.…</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -3292,19 +3292,19 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade och vidgade kunskaper i svenska som andrasp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar kunskaper och färdigheter för att kunna kommunicera…</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -3325,19 +3325,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att ge grundläggande kunskaper i arabisk grammatik och litteratur med didaktiskt fokus.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade och vidgade kunskaper i svenska som andrasp…</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -3358,19 +3358,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att ge grundläggande kunskaper i arabisk grammatik och litteratur med didaktiskt fokus.…</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -3391,19 +3391,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -3424,19 +3424,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade och vidgade kunskaper i svenska som andrasp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -3457,19 +3457,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i arabiska som modersmål med didaktiskt fokus.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade och vidgade kunskaper i svenska som andrasp…</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSS39P</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -3490,19 +3490,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande orienterar sig om andraspråksforskning och forskning om svenska som and…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i arabiska som modersmål med didaktiskt fokus.…</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GSS39Q</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3523,19 +3523,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande fördjupar sig i ett kunskapsområde inom ramen för andraspråksforskning …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande orienterar sig om andraspråksforskning och forskning om svenska som and…</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS39Q</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3556,19 +3556,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande fördjupar sig i ett kunskapsområde inom ramen för andraspråksforskning …</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -3589,19 +3589,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är indelade per delkurs.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3622,19 +3622,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är indelade per delkurs.…</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -3655,19 +3655,19 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -3688,19 +3688,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -3721,19 +3721,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i ämnet modersmål med didaktiskt fokus. Därutöve…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3754,19 +3754,19 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i ämnet modersmål med didaktiskt fokus. Därutöve…</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3787,19 +3787,19 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -3820,19 +3820,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper inom Svenska som andr…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3853,29 +3853,29 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Se respektive delkurs…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper inom Svenska som andr…</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2013-02-04</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -3886,19 +3886,19 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Se respektive delkurs…</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ASV2A2</t>
+          <t>ASV29Z</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3924,14 +3924,14 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSV2P9</t>
+          <t>ASV2A2</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -3952,19 +3952,19 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>GSV2P9</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -3985,19 +3985,19 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet…</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4023,14 +4023,14 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4051,19 +4051,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -4117,19 +4117,19 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper om språkliga och innehållsliga möns…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4150,19 +4150,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande uppnår fördjupade kunskaper om språk och skönlitteratur i relation till s…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper om språkliga och innehållsliga möns…</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4183,19 +4183,19 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bredda sitt kunnande om forsknings- och utvecklingsarbete inom litter…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande uppnår fördjupade kunskaper om språk och skönlitteratur i relation till s…</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -4216,29 +4216,29 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar teoretiska och didaktiska kunskaper om barns språk-, l…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bredda sitt kunnande om forsknings- och utvecklingsarbete inom litter…</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -4249,19 +4249,19 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar teoretiska och didaktiska kunskaper om barns språk-, l…</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>ATY255</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4287,14 +4287,14 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>ATY256</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -4315,19 +4315,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i teorier kring genus och identitet och hur…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -4348,19 +4348,19 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till tyskspråkig barn- och ungdomslitteratur med tonvikt på samtida texter. Litteratur i olik…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i teorier kring genus och identitet och hur…</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -4381,19 +4381,19 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper in…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till tyskspråkig barn- och ungdomslitteratur med tonvikt på samtida texter. Litteratur i olik…</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -4414,19 +4414,19 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i tysk grammatik och färdigheter i …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper in…</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GTY2SU</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4447,19 +4447,19 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i allmän och tysk grammatik samt fä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i tysk grammatik och färdigheter i …</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GTY2SW</t>
+          <t>GTY2SU</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4480,19 +4480,19 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska förvärva en inblick i modern tyskspråkig litteratur. Efter genomgången kurs ska…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i allmän och tysk grammatik samt fä…</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SU</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GTY2SY</t>
+          <t>GTY2SW</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4513,19 +4513,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla sitt kreativa skrivande och sin förmåga att uttrycka sig korrekt, vari…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska förvärva en inblick i modern tyskspråkig litteratur. Efter genomgången kurs ska…</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GTY2SZ</t>
+          <t>GTY2SY</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4546,19 +4546,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska. Den studerande…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla sitt kreativa skrivande och sin förmåga att uttrycka sig korrekt, vari…</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SY</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GTY2W5</t>
+          <t>GTY2SZ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -4579,19 +4579,19 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt på…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska. Den studerande…</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2W5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SZ</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GTY369</t>
+          <t>GTY2W5</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -4612,19 +4612,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska samt förvärva e…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt på…</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY369</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2W5</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY369</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2023-09-08</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4645,19 +4645,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det tyska språket, om tyskspråkig kultur och litter…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska samt förvärva e…</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY369</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4678,19 +4678,19 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det tyska språket, om tyskspråkig kultur och litter…</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -4716,14 +4716,14 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4744,19 +4744,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studenten fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper inom ty…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska…</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>TY1038</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4766,14 +4766,10 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2011-10-10</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4781,19 +4777,19 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i språkdidaktik och att de förbereder sig för sin fra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studenten fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper inom ty…</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>TY1038</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4803,12 +4799,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2011-10-10</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2013-08-01</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4818,19 +4814,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska lära känna ett antal tyskspråkiga litterära verk från upplysningen och fram till …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i språkdidaktik och att de förbereder sig för sin fra…</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>TY1049</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4845,7 +4841,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2013-08-01</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -4855,19 +4851,19 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande skall befästa och ytterligare förbättra förmågan att använda det tyska språket i sk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska lära känna ett antal tyskspråkiga litterära verk från upplysningen och fram till …</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>TY1050</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4877,7 +4873,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4892,19 +4888,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokument samt att de…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande skall befästa och ytterligare förbättra förmågan att använda det tyska språket i sk…</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4914,10 +4910,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2016-02-11</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>2013-11-04</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4925,19 +4925,19 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förvärva en djupare inblick i tysk språk- och kulturhistoria och skaffa sig en…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokument samt att de…</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4947,7 +4947,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2017-02-13</t>
+          <t>2016-02-11</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -4958,19 +4958,19 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förbättra sin förmåga att uttrycka sig ledigt och korrekt på tyska. Den studer…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förvärva en djupare inblick i tysk språk- och kulturhistoria och skaffa sig en…</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>TY2004</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4980,14 +4980,10 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2008-05-29</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2013-08-01</t>
-        </is>
-      </c>
+          <t>2017-02-13</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4995,19 +4991,19 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna tillägnar sig en ökad litteraturvetenskaplig orientering med utgångspunkt i den tysks…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förbättra sin förmåga att uttrycka sig ledigt och korrekt på tyska. Den studer…</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY2004</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5017,12 +5013,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
+          <t>2008-05-29</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2013-08-01</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5032,19 +5028,19 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att studenterna ytterligare ska uppöva sin förmåga till vetenskapligt arbete.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna tillägnar sig en ökad litteraturvetenskaplig orientering med utgångspunkt i den tysks…</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY2007</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5069,19 +5065,19 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva vidgade insikter i den moderna tyska språkvetenskapens utveckling. Kurse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att studenterna ytterligare ska uppöva sin förmåga till vetenskapligt arbete.…</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>TY2008</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5091,7 +5087,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2012-05-21</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -5106,19 +5102,19 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva väsentligt fördjupade insikter i det tyska språkets struktur och variati…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva vidgade insikter i den moderna tyska språkvetenskapens utveckling. Kurse…</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>TY3012</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5133,7 +5129,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2023-12-08</t>
+          <t>2019-12-20</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5143,19 +5139,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i den tyska moderna kvinnolitteraturen. Det…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva väsentligt fördjupade insikter i det tyska språkets struktur och variati…</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>TY3013</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5180,54 +5176,91 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att närmare belysa och problematisera begreppen intertextualitet och intermedialitet. Med utgångspunkt …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i den tyska moderna kvinnolitteraturen. Det…</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att närmare belysa och problematisera begreppen intertextualitet och intermedialitet. Med utgångspunkt …</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B143" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C143" t="inlineStr">
         <is>
           <t>2014-01-27</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D143" t="inlineStr">
         <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva fördjupade insikter om…</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G142"/>
+  <autoFilter ref="A1:G143"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -5511,6 +5544,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G141" r:id="rId280"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A142" r:id="rId281"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId284"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/04 ISLL/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/04 ISLL/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$149</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2236,17 +2236,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AKI25K</t>
+          <t>GIT3KL</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KIA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2020-03-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2257,19 +2257,19 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om barn- och ungdomsskildringar i italiensk skönlitter…</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIT3KL</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GKI27M</t>
+          <t>AKI25K</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2019-03-08</t>
+          <t>2020-03-12</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -2290,19 +2290,19 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AKI25K</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GKI2MY</t>
+          <t>GKI27M</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2021-03-02</t>
+          <t>2019-03-08</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -2323,19 +2323,19 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i det kinesiska språket, vilket förbere…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att utveckla…</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI27M</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GKI2PY</t>
+          <t>GKI2MY</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2021-05-03</t>
+          <t>2021-03-02</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -2356,19 +2356,19 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att hjälpa studenterna att befästa de kunskaper de tillgodogjort sig på kurserna på lägre nivå i kine…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper i det kinesiska språket, vilket förbere…</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2MY</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GKI2W3</t>
+          <t>GKI2PY</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-05-03</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -2389,19 +2389,19 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen ämnar att ge den studerande grundläggande kunskaper i det kinesiska språket, vilket förbereder den studerande inf…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att hjälpa studenterna att befästa de kunskaper de tillgodogjort sig på kurserna på lägre nivå i kine…</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2PY</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GKI3CE</t>
+          <t>GKI2W3</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -2422,19 +2422,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka och vidareutveckla den studerandes språkfärdighet i kinesiska. Kursen ämnar även …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ämnar att ge den studerande grundläggande kunskaper i det kinesiska språket, vilket förbereder den studerande inf…</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI2W3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>KI1030</t>
+          <t>GKI3CE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2444,14 +2444,10 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2011-02-01</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2459,32 +2455,36 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att stärka och ytterligare utveckla studenternas språkfärdighet inom det kinesiska språket, i de fyra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att stärka och vidareutveckla den studerandes språkfärdighet i kinesiska. Kursen ämnar även …</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GKI3CE</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GPR3GM</t>
+          <t>KI1030</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>KIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>2011-02-01</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2013-11-04</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2492,19 +2492,19 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att stärka och ytterligare utveckla studenternas språkfärdighet inom det kinesiska språket, i de fyra…</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=KI1030</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GPR3GN</t>
+          <t>GPR3GM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2530,14 +2530,14 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GM</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GPR3GP</t>
+          <t>GPR3GN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2563,24 +2563,24 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GRY2YW</t>
+          <t>GPR3GP</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RYA</t>
+          <t>PRA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2022-11-29</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -2591,19 +2591,19 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren efter avslutad kurs har utvecklat kunskaper, färdigheter och förhållnings…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': -…</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2YW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GPR3GP</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GRY325</t>
+          <t>GRY2YW</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2022-11-29</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -2624,29 +2624,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om den ryska operans utveckling från 1917 och fra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren efter avslutad kurs har utvecklat kunskaper, färdigheter och förhållnings…</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY2YW</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ASP25D</t>
+          <t>GRY325</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SPA</t>
+          <t>RYA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -2657,19 +2657,19 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i spanska och sin teoretiska medvetenhet i…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om den ryska operans utveckling från 1917 och fra…</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GRY325</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ASP25E</t>
+          <t>ASP25D</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25D</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GSP28C</t>
+          <t>ASP25E</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2019-03-13</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -2723,19 +2723,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur och spansk ling…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar såväl sina kunskaper i spanska och sin teoretiska medvetenhet i…</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASP25E</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GSP2FQ</t>
+          <t>GSP28C</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2745,14 +2745,10 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2025-06-02</t>
-        </is>
-      </c>
+          <t>2019-03-13</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2760,19 +2756,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur och spansk ling…</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP28C</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GSP2FR</t>
+          <t>GSP2FQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2782,10 +2778,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>2020-02-26</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2793,19 +2793,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokumen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FQ</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>GSP2JH</t>
+          <t>GSP2FR</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2020-09-21</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -2826,19 +2826,19 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokumen…</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2FR</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GSP2SK</t>
+          <t>GSP2JH</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2021-12-10</t>
+          <t>2020-09-21</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -2859,19 +2859,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten utvecklar kunskaper om den spansktalande världens kultur och samhällsförhållanden samt …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande…</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2JH</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>GSP2W6</t>
+          <t>GSP2SK</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-12-10</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -2892,19 +2892,19 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten utvecklar kunskaper om den spansktalande världens kultur och samhällsförhållanden samt …</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2SK</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>GSP2W7</t>
+          <t>GSP2W6</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2925,19 +2925,19 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion till språkdidaktik. Kursen ger en teoretisk grund till språklär…</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>GSP2W8</t>
+          <t>GSP2W7</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2950,11 +2950,7 @@
           <t>2022-04-28</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2023-11-02</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2962,19 +2958,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion i och förberedelse för sin blivande yrkesroll som spansklärare …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen…</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SP1051</t>
+          <t>GSP2W8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2984,10 +2980,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -2995,19 +2995,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att ge den studerande en introduktion i och förberedelse för sin blivande yrkesroll som spansklärare …</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP2W8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SP1052</t>
+          <t>GSP3KS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -3028,19 +3028,19 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar goda…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KS</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SP1053</t>
+          <t>GSP3KT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2017-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -3061,19 +3061,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studenten utvecklar goda kunskaper i spansk litteratur och film i relation till det spanska samhället…</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KT</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SP2021</t>
+          <t>GSP3KV</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Genom studiet av relevant litteraturteori och -historia utvecklar studenten sin förmåga att analysera och kritiskt grans…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar grundläggande kunskaper i spansk lingvistik, inbegripet områdena språkutveck…</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSP3KV</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SP2022</t>
+          <t>SP1051</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -3127,19 +3127,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål…</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1051</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SP2023</t>
+          <t>SP1052</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2018-02-12</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -3160,29 +3160,29 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar goda…</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1052</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GSS2FK</t>
+          <t>SP1053</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2020-03-10</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -3193,29 +3193,29 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP1053</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GSS2G8</t>
+          <t>SP2021</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2020-04-01</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -3226,29 +3226,29 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Genom studiet av relevant litteraturteori och -historia utvecklar studenten sin förmåga att analysera och kritiskt grans…</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2021</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GSS2GP</t>
+          <t>SP2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2020-04-27</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -3259,29 +3259,29 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina didaktiska kunskaper i arabiska som modersmål.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2022</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>GSS2J5</t>
+          <t>SP2023</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>SPA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2020-09-09</t>
+          <t>2018-02-12</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -3292,19 +3292,19 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar kunskaper och färdigheter för att kunna kommunicera…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande utvecklar fördjupade kunskaper i spanskspråkig litteratur samt en förmåga att analyser…</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SP2023</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GSS2JA</t>
+          <t>GSS2FK</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2020-09-14</t>
+          <t>2020-03-10</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -3325,19 +3325,19 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade och vidgade kunskaper i svenska som andrasp…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2FK</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GSS2L2</t>
+          <t>GSS2G8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2020-12-01</t>
+          <t>2020-04-01</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -3358,19 +3358,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att ge grundläggande kunskaper i arabisk grammatik och litteratur med didaktiskt fokus.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina…</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2G8</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GSS2MN</t>
+          <t>GSS2GP</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2020-04-27</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -3391,19 +3391,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina didaktiska kunskaper i arabiska som modersmål.…</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2GP</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>GSS2QV</t>
+          <t>GSS2J5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2021-06-30</t>
+          <t>2020-09-09</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -3424,19 +3424,19 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar kunskaper och färdigheter för att kunna kommunicera…</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2J5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GSS2XE</t>
+          <t>GSS2JA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2022-09-02</t>
+          <t>2020-09-14</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -3462,14 +3462,14 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2JA</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>GSS35H</t>
+          <t>GSS2L2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2020-12-01</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -3490,19 +3490,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i arabiska som modersmål med didaktiskt fokus.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att ge grundläggande kunskaper i arabisk grammatik och litteratur med didaktiskt fokus.…</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2L2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GSS39P</t>
+          <t>GSS2MN</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2021-02-25</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -3523,19 +3523,19 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande orienterar sig om andraspråksforskning och forskning om svenska som and…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2MN</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>GSS39Q</t>
+          <t>GSS2QV</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2021-06-30</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -3556,19 +3556,19 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande fördjupar sig i ett kunskapsområde inom ramen för andraspråksforskning …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2QV</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>GSS39R</t>
+          <t>GSS2XE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2022-09-02</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -3589,19 +3589,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar fördjupade och vidgade kunskaper i svenska som andrasp…</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS2XE</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GSS3BL</t>
+          <t>GSS35H</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2023-06-27</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -3622,19 +3622,19 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är indelade per delkurs.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i arabiska som modersmål med didaktiskt fokus.…</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS35H</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>GSS3BN</t>
+          <t>GSS39P</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3644,10 +3644,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -3655,19 +3659,19 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande orienterar sig om andraspråksforskning och forskning om svenska som and…</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39P</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GSS3C7</t>
+          <t>GSS39Q</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3677,10 +3681,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -3688,19 +3696,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande syfte är att den studerande fördjupar sig i ett kunskapsområde inom ramen för andraspråksforskning …</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39Q</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>GSS3H8</t>
+          <t>GSS39R</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3710,10 +3718,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -3721,19 +3733,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS39R</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GSS3HB</t>
+          <t>GSS3BL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3743,7 +3755,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -3754,19 +3766,19 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i ämnet modersmål med didaktiskt fokus. Därutöve…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är indelade per delkurs.…</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BL</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GSS3HG</t>
+          <t>GSS3BN</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3776,7 +3788,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -3787,19 +3799,19 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3BN</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GSS3HJ</t>
+          <t>GSS3C7</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3809,10 +3821,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -3820,19 +3836,19 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3C7</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>SS1085</t>
+          <t>GSS3H8</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3842,7 +3858,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2015-03-03</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -3853,19 +3869,19 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper inom Svenska som andr…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3H8</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SS2009</t>
+          <t>GSS3HB</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3875,7 +3891,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2013-02-04</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -3886,29 +3902,29 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Se respektive delkurs…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i ämnet modersmål med didaktiskt fokus. Därutöve…</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HB</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ASV29Z</t>
+          <t>GSS3HG</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
@@ -3919,29 +3935,29 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar…</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HG</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>ASV2A2</t>
+          <t>GSS3HJ</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2023-12-04</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -3952,29 +3968,29 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper ino…</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSS3HJ</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>GSV2P9</t>
+          <t>SS1085</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2021-04-12</t>
+          <t>2015-03-03</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -3985,32 +4001,36 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Målet med kursen är att den studerande utvecklar sina ämneskunskaper och ämnesdidaktiska kunskaper inom Svenska som andr…</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS1085</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZU</t>
+          <t>SS2009</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SVE</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>2013-02-04</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4018,19 +4038,19 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Se respektive delkurs…</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SS2009</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZV</t>
+          <t>ASV29Z</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4040,7 +4060,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -4051,19 +4071,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV29Z</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZW</t>
+          <t>ASV2A2</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4073,7 +4093,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2023-12-04</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -4084,19 +4104,19 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna genomföra en kvalificerad och självständig vetenskaplig undersö…</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASV2A2</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GSV2ZX</t>
+          <t>GSV2P9</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4106,7 +4126,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2023-01-23</t>
+          <t>2021-04-12</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -4117,19 +4137,19 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet…</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2P9</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GSV3DD</t>
+          <t>GSV2ZU</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4139,7 +4159,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -4150,19 +4170,19 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper om språkliga och innehållsliga möns…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZU</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GSV3DE</t>
+          <t>GSV2ZV</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4172,7 +4192,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -4183,19 +4203,19 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande uppnår fördjupade kunskaper om språk och skönlitteratur i relation till s…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om barns språk, språkkompetens, språkut…</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZV</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GSV3DF</t>
+          <t>GSV2ZW</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4205,7 +4225,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -4216,19 +4236,19 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bredda sitt kunnande om forsknings- och utvecklingsarbete inom litter…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZW</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>GSV3JE</t>
+          <t>GSV2ZX</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4238,7 +4258,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2023-01-23</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
@@ -4249,29 +4269,29 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar teoretiska och didaktiska kunskaper om barns språk-, l…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar fördjupad kunskap om barns skriftspråksutveckling, grundläggand…</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV2ZX</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>ATY255</t>
+          <t>GSV3DD</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -4282,29 +4302,29 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper om språkliga och innehållsliga möns…</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DD</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ATY256</t>
+          <t>GSV3DE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2020-03-11</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -4315,29 +4335,29 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande uppnår fördjupade kunskaper om språk och skönlitteratur i relation till s…</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DE</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ATY2B8</t>
+          <t>GSV3DF</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -4348,29 +4368,29 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i teorier kring genus och identitet och hur…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska bredda sitt kunnande om forsknings- och utvecklingsarbete inom litter…</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3DF</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GTY23C</t>
+          <t>GSV3JE</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -4381,29 +4401,29 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till tyskspråkig barn- och ungdomslitteratur med tonvikt på samtida texter. Litteratur i olik…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande utvecklar teoretiska och didaktiska kunskaper om barns språk-, l…</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3JE</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GTY2N5</t>
+          <t>GSV3KH</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>TYA</t>
+          <t>SVE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2021-03-04</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -4414,19 +4434,19 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper in…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar kunskaper om elevers läs- och skrivutveckling utifrån ett först…</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSV3KH</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>GTY2ST</t>
+          <t>ATY255</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4436,7 +4456,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -4447,19 +4467,19 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i tysk grammatik och färdigheter i …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY255</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GTY2SU</t>
+          <t>ATY256</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4469,7 +4489,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2020-03-11</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -4480,19 +4500,19 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i allmän och tysk grammatik samt fä…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska genomföra en kvalificerad och självständig vetenskaplig undersökning …</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY256</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>GTY2SW</t>
+          <t>ATY2B8</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4502,7 +4522,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -4513,19 +4533,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska förvärva en inblick i modern tyskspråkig litteratur. Efter genomgången kurs ska…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i teorier kring genus och identitet och hur…</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ATY2B8</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GTY2SY</t>
+          <t>GTY23C</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4535,7 +4555,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2018-06-05</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -4546,19 +4566,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla sitt kreativa skrivande och sin förmåga att uttrycka sig korrekt, vari…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen ger en introduktion till tyskspråkig barn- och ungdomslitteratur med tonvikt på samtida texter. Litteratur i olik…</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY23C</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GTY2SZ</t>
+          <t>GTY2N5</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4568,7 +4588,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>2021-03-04</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -4579,19 +4599,19 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska. Den studerande…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att den studerande fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper in…</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SZ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2N5</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>GTY2W5</t>
+          <t>GTY2ST</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4601,7 +4621,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2022-04-28</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -4612,19 +4632,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt på…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i tysk grammatik och färdigheter i …</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2W5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2ST</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GTY369</t>
+          <t>GTY2SU</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4634,7 +4654,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2023-09-08</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -4645,19 +4665,19 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska samt förvärva e…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla grundläggande teoretiska kunskaper i allmän och tysk grammatik samt fä…</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY369</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SU</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GTY3CT</t>
+          <t>GTY2SW</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4667,7 +4687,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -4678,19 +4698,19 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det tyska språket, om tyskspråkig kultur och litter…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska förvärva en inblick i modern tyskspråkig litteratur. Efter genomgången kurs ska…</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SW</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>GTY3CU</t>
+          <t>GTY2SY</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4700,7 +4720,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-11-13</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -4711,19 +4731,19 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande ska utveckla sitt kreativa skrivande och sin förmåga att uttrycka sig korrekt, vari…</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SY</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>GTY3J9</t>
+          <t>GTY2SZ</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4733,7 +4753,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2021-12-16</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -4744,19 +4764,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska. Den studerande…</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2SZ</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>GTY3JB</t>
+          <t>GTY2W5</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4766,7 +4786,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2022-04-28</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -4777,19 +4797,19 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studenten fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper inom ty…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att utveckla förmågan att kommunicera skriftligt på…</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY2W5</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TY1038</t>
+          <t>GTY369</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4799,14 +4819,10 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2011-10-10</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2020-07-02</t>
-        </is>
-      </c>
+          <t>2023-09-08</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4814,19 +4830,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i språkdidaktik och att de förbereder sig för sin fra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska utveckla grundläggande färdigheter i att tala och förstå tyska samt förvärva e…</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY369</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>TY1049</t>
+          <t>GTY3CT</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4836,14 +4852,10 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2013-08-01</t>
-        </is>
-      </c>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4851,19 +4863,19 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska lära känna ett antal tyskspråkiga litterära verk från upplysningen och fram till …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det tyska språket, om tyskspråkig kultur och litter…</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CT</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>TY1050</t>
+          <t>GTY3CU</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4873,14 +4885,10 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2012-05-21</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2024-11-13</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4888,19 +4896,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande skall befästa och ytterligare förbättra förmågan att använda det tyska språket i sk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska…</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3CU</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>TY1066</t>
+          <t>GTY3J9</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4910,14 +4918,10 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2013-11-04</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2019-12-20</t>
-        </is>
-      </c>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -4925,19 +4929,19 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokument samt att de…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande fördjupar sina kunskaper i det tyska…</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3J9</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>TY1069</t>
+          <t>GTY3JB</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4947,7 +4951,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2016-02-11</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -4958,19 +4962,19 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förvärva en djupare inblick i tysk språk- och kulturhistoria och skaffa sig en…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att studenten fördjupar såväl sina språkfärdigheter i tyska språket som sina teoretiska kunskaper inom ty…</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3JB</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>TY1073</t>
+          <t>GTY3KG</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4980,7 +4984,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2017-02-13</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -4991,19 +4995,19 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förbättra sin förmåga att uttrycka sig ledigt och korrekt på tyska. Den studer…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i det tyska språket, om tyskspråkig kultur och litter…</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GTY3KG</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>TY2004</t>
+          <t>TY1038</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5013,12 +5017,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2008-05-29</t>
+          <t>2011-10-10</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2013-08-01</t>
+          <t>2020-07-02</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5028,19 +5032,19 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna tillägnar sig en ökad litteraturvetenskaplig orientering med utgångspunkt i den tysks…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande utvecklar grundläggande kunskaper i språkdidaktik och att de förbereder sig för sin fra…</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1038</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>TY2007</t>
+          <t>TY1049</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5055,7 +5059,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2019-12-20</t>
+          <t>2013-08-01</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5065,19 +5069,19 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att studenterna ytterligare ska uppöva sin förmåga till vetenskapligt arbete.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska lära känna ett antal tyskspråkiga litterära verk från upplysningen och fram till …</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1049</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>TY2008</t>
+          <t>TY1050</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5102,19 +5106,19 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva vidgade insikter i den moderna tyska språkvetenskapens utveckling. Kurse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att de studerande skall befästa och ytterligare förbättra förmågan att använda det tyska språket i sk…</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1050</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TY3012</t>
+          <t>TY1066</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5124,7 +5128,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
+          <t>2013-11-04</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -5139,19 +5143,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva väsentligt fördjupade insikter i det tyska språkets struktur och variati…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens mål är att de studerande fördjupar sina kunskaper i språkdidaktiska teorier och skolans styrdokument samt att de…</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1066</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>TY3013</t>
+          <t>TY1069</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5161,14 +5165,10 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2016-02-11</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -5176,19 +5176,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i den tyska moderna kvinnolitteraturen. Det…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förvärva en djupare inblick i tysk språk- och kulturhistoria och skaffa sig en…</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1069</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TY3015</t>
+          <t>TY1073</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5198,14 +5198,10 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2013-11-07</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2023-12-08</t>
-        </is>
-      </c>
+          <t>2017-02-13</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
           <t>Prosa/rubrik före frasning</t>
@@ -5213,54 +5209,276 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att närmare belysa och problematisera begreppen intertextualitet och intermedialitet. Med utgångspunkt …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att den studerande ska förbättra sin förmåga att uttrycka sig ledigt och korrekt på tyska. Den studer…</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY1073</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>TY2004</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2008-05-29</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna tillägnar sig en ökad litteraturvetenskaplig orientering med utgångspunkt i den tysks…</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2004</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>TY2007</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att studenterna ytterligare ska uppöva sin förmåga till vetenskapligt arbete.…</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2007</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>TY2008</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2012-05-21</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva vidgade insikter i den moderna tyska språkvetenskapens utveckling. Kurse…</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY2008</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>TY3012</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2019-12-20</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenterna ska förvärva väsentligt fördjupade insikter i det tyska språkets struktur och variati…</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>TY3013</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva väsentligt fördjupade insikter i den tyska moderna kvinnolitteraturen. Det…</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>TY3015</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>TYA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2013-11-07</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2023-12-08</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens syfte är att närmare belysa och problematisera begreppen intertextualitet och intermedialitet. Med utgångspunkt …</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
           <t>TY3016</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B149" t="inlineStr">
         <is>
           <t>TYA</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>2014-01-27</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>2023-12-08</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen syftar till att studenten ska förvärva fördjupade insikter om…</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=TY3016</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G143"/>
+  <autoFilter ref="A1:G149"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -5546,6 +5764,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G142" r:id="rId282"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId283"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G143" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G144" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G145" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G146" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G147" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G148" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G149" r:id="rId296"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
